--- a/Sindhi Muslim/People Diary/December-2024.xlsx
+++ b/Sindhi Muslim/People Diary/December-2024.xlsx
@@ -8,24 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\People Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E02FA05D-AA05-40D8-87EA-095F8F11ADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2457D430-3A24-4F5C-A0B6-CF7F4E65B2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="01-12-2024" sheetId="1" r:id="rId1"/>
+    <sheet name="02-12-2024" sheetId="1" r:id="rId1"/>
+    <sheet name="03-12-2024" sheetId="2" r:id="rId2"/>
+    <sheet name="04-12-2024" sheetId="3" r:id="rId3"/>
+    <sheet name="05-12-2024" sheetId="6" r:id="rId4"/>
+    <sheet name="06-12-2024" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="26">
   <si>
     <t>CLASS WISE ENROLLED SUMMARY</t>
   </si>
@@ -46,9 +59,6 @@
   </si>
   <si>
     <t>PERCENTAGE</t>
-  </si>
-  <si>
-    <t>ECE</t>
   </si>
   <si>
     <t>ONE</t>
@@ -81,10 +91,31 @@
     <t>Monthly Attendance Summary of Student GHS</t>
   </si>
   <si>
-    <t>Enrollment (01-12-2024)</t>
+    <t>ECE (ROSE)</t>
+  </si>
+  <si>
+    <t>ECE (Daffodils)</t>
   </si>
   <si>
     <t>SJCHS (December-2024)</t>
+  </si>
+  <si>
+    <t>Enrollment (02-12-2024) (Monday)</t>
+  </si>
+  <si>
+    <t>SJCHS (Decenber-2024)</t>
+  </si>
+  <si>
+    <t>Enrollment (03-12-2024) (Tuesday)</t>
+  </si>
+  <si>
+    <t>Enrollment (04-12-2024) (Wednesday)</t>
+  </si>
+  <si>
+    <t>Enrollment (05-12-2024) (Thursday)</t>
+  </si>
+  <si>
+    <t>Enrollment (06-12-2024) (Friday)</t>
   </si>
 </sst>
 </file>
@@ -150,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -189,21 +220,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -393,50 +409,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -446,10 +449,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -461,9 +464,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,10 +745,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -758,202 +759,1972 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="24" t="s">
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>43</v>
+      </c>
+      <c r="H5" s="24">
+        <f t="shared" ref="H5:H15" si="1">G5/D5*100</f>
+        <v>79.629629629629633</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="26"/>
-    </row>
-    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="3"/>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f>B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" si="1"/>
+        <v>92.857142857142861</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" ref="D7:D15" si="2">B7+C7</f>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>46</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="1"/>
+        <v>83.636363636363626</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>45</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="1"/>
+        <v>86.538461538461547</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>22</v>
+      </c>
+      <c r="F9" s="1">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>76.923076923076934</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="3"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
         <v>16</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13"/>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A76C6F-7346-4E3E-9D3A-7A332125E520}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>43</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>79.629629629629633</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f>B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="1">G6/D6*100</f>
+        <v>92.857142857142861</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" ref="D6:D7" si="2">B7+C7</f>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>53</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="1"/>
+        <v>96.36363636363636</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" ref="D8:D15" si="3">B8+C8</f>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="4">E8+F8</f>
+        <v>47</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="1"/>
+        <v>90.384615384615387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="4"/>
+        <v>47</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>90.384615384615387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="15"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{943B4986-70E4-4CC7-A180-52208B012F00}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>45</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>94.642857142857139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>52</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>94.545454545454547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>47</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>90.384615384615387</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>92.307692307692307</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="16"/>
-      <c r="F16" s="15"/>
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4D9A89E-912D-48EC-B0C6-0C6843B2EE85}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>27</v>
+      </c>
+      <c r="F5" s="4">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>45</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>89.285714285714292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>52</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>94.545454545454547</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>23</v>
+      </c>
+      <c r="F8" s="1">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>46</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>88.461538461538453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>24</v>
+      </c>
+      <c r="F9" s="1">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>90.384615384615387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2154D1D2-18FC-4FA4-A9C0-DA69DB8B27FA}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>45</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>89.285714285714292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>26</v>
+      </c>
+      <c r="F7" s="1">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>45</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>21</v>
+      </c>
+      <c r="F8" s="1">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>42</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>80.769230769230774</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>20</v>
+      </c>
+      <c r="F9" s="1">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>73.076923076923066</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11">
+        <f>SUM(D5:D15)</f>
+        <v>531</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
